--- a/docs/tableau_synthese.xlsx
+++ b/docs/tableau_synthese.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f78ac8c4115f8c98/Bureau/Cours/Info/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f78ac8c4115f8c98/Documents/_Bureau/BTS SIO - Nextech/Info/E5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="13_ncr:1_{D8954446-012C-4161-BD63-AF49C01CCF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C365CD72-27B1-459F-B008-6043A75B362C}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="8_{181E88D1-149F-4158-ABF1-535095BE27AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8105D1CB-C0B9-405A-AC8D-2DD81F8DEC3A}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="-120" windowWidth="37560" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
+    <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E4'!$A$1:$H$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$35</definedName>
   </definedNames>
   <calcPr calcId="101716"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="55">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -98,9 +98,6 @@
 (intitulé et liste des documents et productions associés)</t>
   </si>
   <si>
-    <t>SESSION 2022</t>
-  </si>
-  <si>
     <t>Période (sous la forme du JJ/MM/AA au JJ/MM/AA)</t>
   </si>
   <si>
@@ -110,22 +107,13 @@
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
+    <t>SESSION 2026</t>
+  </si>
+  <si>
     <t>NOM et prénom : RODRIGUEZ-MONTEAGUDO Christopher</t>
   </si>
   <si>
-    <t>Centre de formation : IFC MARSEILLE</t>
-  </si>
-  <si>
-    <t>Intervention sur poste informatique</t>
-  </si>
-  <si>
-    <t>Installation poste sécuriser</t>
-  </si>
-  <si>
-    <t>Installation switch</t>
-  </si>
-  <si>
-    <t>Site portfolio : https://christopherrodriguezbts2023.wordpress.com</t>
+    <t>N° candidat : 02244125460</t>
   </si>
   <si>
     <r>
@@ -152,49 +140,94 @@
     </r>
   </si>
   <si>
-    <t>N° candidat : 02244125460</t>
-  </si>
-  <si>
-    <t>Installation ordinateur</t>
-  </si>
-  <si>
-    <t>Installation VPN</t>
-  </si>
-  <si>
-    <t>Prise de main à distance</t>
-  </si>
-  <si>
-    <t>Installation de serveur windows</t>
-  </si>
-  <si>
-    <t>Configuration switch</t>
-  </si>
-  <si>
-    <t>Installation application</t>
-  </si>
-  <si>
-    <t>Gestion parc informatique</t>
-  </si>
-  <si>
-    <t>Installation serveur artica</t>
-  </si>
-  <si>
-    <t>installation serveur exchange</t>
-  </si>
-  <si>
-    <t>installation serveur asterisk</t>
-  </si>
-  <si>
-    <t>Installation serveur proxmox</t>
-  </si>
-  <si>
-    <t>installation serveur proxmox backup</t>
-  </si>
-  <si>
-    <t>Installation pfsense</t>
-  </si>
-  <si>
-    <t>P</t>
+    <t>Adresse URL du portfolio : https://www.christopher-rodriguez-monteagudo.fr/</t>
+  </si>
+  <si>
+    <t>Suppression configuration switch pour broker</t>
+  </si>
+  <si>
+    <t>Maintenance des PDA avec compte AD et licence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mise en place switch </t>
+  </si>
+  <si>
+    <t>Vérification des KPI cyber</t>
+  </si>
+  <si>
+    <t>Installation de poste informatique laboratoire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mise en place infrastructure </t>
+  </si>
+  <si>
+    <t>Configuration switch Cisco</t>
+  </si>
+  <si>
+    <t>Configuration routeur Cisco</t>
+  </si>
+  <si>
+    <t>Mise en place solution de sauvegade Proxmox Backup Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installation gestion de ticket (GLPI) </t>
+  </si>
+  <si>
+    <t>Mise en place de solution de super vision</t>
+  </si>
+  <si>
+    <t>Mise en place de firewall physique et virtuel</t>
+  </si>
+  <si>
+    <t>Gestion du parc informatique (Service Now)</t>
+  </si>
+  <si>
+    <t>Gestion de sauvegarde et restauration (Externalisation de bande LTO avec Dataprotector)</t>
+  </si>
+  <si>
+    <t>Mise en place Graylog</t>
+  </si>
+  <si>
+    <t>01/04/2026 au 11/04/2026</t>
+  </si>
+  <si>
+    <t>01/12/2025 au 01/02/2026</t>
+  </si>
+  <si>
+    <t>12/01/2026 au 13/01/2026</t>
+  </si>
+  <si>
+    <t>09/02/2026 au 10/02/2026</t>
+  </si>
+  <si>
+    <t>12/01/2026 au 16/01/2026</t>
+  </si>
+  <si>
+    <t>01/12/2025  au 01/02/2026</t>
+  </si>
+  <si>
+    <t>04/11/2024 au 01/01/2026</t>
+  </si>
+  <si>
+    <t>04/11/2024 au 08/04/2026</t>
+  </si>
+  <si>
+    <t>Vérification des KPI cyber (Extration et croisement des données)</t>
+  </si>
+  <si>
+    <t>☑☑☑☑☑☑</t>
+  </si>
+  <si>
+    <t>☑☑☑</t>
+  </si>
+  <si>
+    <t>☑☑☑☑</t>
+  </si>
+  <si>
+    <t>Centre de formation : AVP CCI - Pertuis</t>
+  </si>
+  <si>
+    <t>☑</t>
   </si>
 </sst>
 </file>
@@ -204,7 +237,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -268,12 +301,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="16"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -294,7 +321,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -451,6 +478,21 @@
       <right style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </right>
+      <top style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom/>
+      <diagonal style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </diagonal>
+    </border>
+    <border diagonalDown="1">
+      <left style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal style="thin">
@@ -520,21 +562,23 @@
       <right style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </right>
+      <top style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
       <top/>
       <bottom style="medium">
         <color theme="2" tint="-0.749992370372631"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -543,7 +587,33 @@
       <top style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -551,59 +621,89 @@
       <right style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color theme="2" tint="-0.749992370372631"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top/>
+      <right/>
+      <top style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
       <bottom style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
+      <left/>
       <right style="medium">
         <color theme="2" tint="-0.749992370372631"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
       <bottom style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color theme="2" tint="-0.749992370372631"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
       </bottom>
       <diagonal/>
     </border>
@@ -611,117 +711,9 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </left>
-      <right style="thin">
-        <color theme="2" tint="-0.749992370372631"/>
-      </right>
-      <top style="medium">
-        <color theme="2" tint="-0.749992370372631"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -729,7 +721,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -738,204 +730,136 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -960,9 +884,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1000,9 +924,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1035,26 +959,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1087,26 +994,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1283,134 +1173,136 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="20.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AQ81"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="118.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="7" customWidth="1"/>
-    <col min="3" max="8" width="18.7109375" style="15" customWidth="1"/>
-    <col min="9" max="43" width="11.42578125" customWidth="1"/>
-    <col min="44" max="16384" width="10.85546875" style="1"/>
+    <col min="1" max="1" width="70.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="43" width="11.44140625" customWidth="1"/>
+    <col min="44" max="16384" width="10.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="34"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="35" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="25"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-    </row>
-    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="37" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+    </row>
+    <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="46"/>
-      <c r="H3" s="47"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="27"/>
+      <c r="H3" s="33"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="19" t="s">
+    <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="21" t="s">
+      <c r="G4" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="19" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="59" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="61"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="48" t="s">
+    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="46"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="57" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="22" t="s">
+      <c r="B6" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="48"/>
-      <c r="B7" s="58"/>
-      <c r="C7" s="17" t="s">
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="35"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="9" t="s">
         <v>14</v>
       </c>
       <c r="I7"/>
@@ -1449,17 +1341,17 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="49" t="s">
+    <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="50"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1496,23 +1388,29 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="65">
-        <v>44593</v>
-      </c>
-      <c r="C9" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="70"/>
+    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>52</v>
+      </c>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1549,25 +1447,23 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="66">
-        <v>44652</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="70"/>
+    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="24"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1604,27 +1500,23 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="64">
-        <v>44470</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="70" t="s">
-        <v>43</v>
-      </c>
+    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="24"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1661,18 +1553,21 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="65">
-        <v>44593</v>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="70"/>
+    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="24"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1709,27 +1604,21 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="66">
-        <v>44531</v>
-      </c>
-      <c r="C13" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H13" s="70" t="s">
-        <v>43</v>
-      </c>
+    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="24"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1766,21 +1655,21 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="67">
-        <v>44882</v>
-      </c>
-      <c r="C14" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="70"/>
+    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="24"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1817,36 +1706,28 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="68">
-        <v>41791</v>
-      </c>
-      <c r="C15" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H15" s="70" t="s">
-        <v>43</v>
-      </c>
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="24"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
       <c r="L15"/>
       <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
       <c r="P15"/>
       <c r="Q15"/>
       <c r="R15"/>
@@ -1876,20 +1757,28 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="12"/>
+    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="24"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
       <c r="L16"/>
       <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
       <c r="P16"/>
       <c r="Q16"/>
       <c r="R16"/>
@@ -1919,20 +1808,22 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="4"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="12"/>
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="11"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="16"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
       <c r="L17"/>
       <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
       <c r="P17"/>
       <c r="Q17"/>
       <c r="R17"/>
@@ -1962,20 +1853,22 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="4"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="12"/>
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="11"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="16"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
       <c r="L18"/>
       <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
       <c r="P18"/>
       <c r="Q18"/>
       <c r="R18"/>
@@ -2005,22 +1898,24 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="53" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="54"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="56"/>
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A19" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
       <c r="L19"/>
       <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
       <c r="P19"/>
       <c r="Q19"/>
       <c r="R19"/>
@@ -2050,32 +1945,28 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="69">
-        <v>44880</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="70" t="s">
-        <v>43</v>
-      </c>
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="16"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20"/>
       <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
       <c r="P20"/>
       <c r="Q20"/>
       <c r="R20"/>
@@ -2105,34 +1996,28 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="69">
-        <v>42156</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="11"/>
-      <c r="F21" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="70" t="s">
-        <v>43</v>
-      </c>
+    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="16"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
       <c r="L21"/>
       <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
       <c r="P21"/>
       <c r="Q21"/>
       <c r="R21"/>
@@ -2162,27 +2047,21 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22" s="69">
-        <v>42156</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="G22" s="11"/>
-      <c r="H22" s="70" t="s">
-        <v>43</v>
-      </c>
+    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="16"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2219,29 +2098,21 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="69">
-        <v>42095</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="11"/>
-      <c r="F23" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="G23" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H23" s="70" t="s">
-        <v>43</v>
-      </c>
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="16"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2278,31 +2149,21 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="69">
-        <v>44228</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="F24" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="G24" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H24" s="70" t="s">
-        <v>43</v>
-      </c>
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="16"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2339,29 +2200,21 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="69">
-        <v>42095</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="G25" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H25" s="70" t="s">
-        <v>43</v>
-      </c>
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="16"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2398,29 +2251,15 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="69">
-        <v>42095</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="G26" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H26" s="70" t="s">
-        <v>43</v>
-      </c>
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="11"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="16"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2457,27 +2296,17 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="69">
-        <v>44256</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="G27" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H27" s="70" t="s">
-        <v>43</v>
-      </c>
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A27" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="41"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2514,17 +2343,21 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A28" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="33"/>
+    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="16"/>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2561,23 +2394,21 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="68">
-        <v>44880</v>
-      </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="F29" s="11"/>
-      <c r="G29" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="H29" s="12"/>
+    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="16"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2614,15 +2445,15 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="28"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="12"/>
+    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="11"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="16"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2659,15 +2490,15 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="28"/>
-      <c r="B31" s="62"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="12"/>
+    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="11"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="16"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2704,15 +2535,15 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="26"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="12"/>
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="11"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="16"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2749,15 +2580,15 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="4"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="12"/>
+    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="11"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="16"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
@@ -2794,15 +2625,15 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="4"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12"/>
+    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="12"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="18"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
@@ -2839,15 +2670,15 @@
       <c r="AP34"/>
       <c r="AQ34"/>
     </row>
-    <row r="35" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="4"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="12"/>
+    <row r="35" spans="1:43" s="2" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A35" s="5"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
       <c r="I35"/>
       <c r="J35"/>
       <c r="K35"/>
@@ -2884,529 +2715,71 @@
       <c r="AP35"/>
       <c r="AQ35"/>
     </row>
-    <row r="36" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="5"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="14"/>
-      <c r="I36"/>
-      <c r="J36"/>
-      <c r="K36"/>
-      <c r="L36"/>
-      <c r="M36"/>
-      <c r="N36"/>
-      <c r="O36"/>
-      <c r="P36"/>
-      <c r="Q36"/>
-      <c r="R36"/>
-      <c r="S36"/>
-      <c r="T36"/>
-      <c r="U36"/>
-      <c r="V36"/>
-      <c r="W36"/>
-      <c r="X36"/>
-      <c r="Y36"/>
-      <c r="Z36"/>
-      <c r="AA36"/>
-      <c r="AB36"/>
-      <c r="AC36"/>
-      <c r="AD36"/>
-      <c r="AE36"/>
-      <c r="AF36"/>
-      <c r="AG36"/>
-      <c r="AH36"/>
-      <c r="AI36"/>
-      <c r="AJ36"/>
-      <c r="AK36"/>
-      <c r="AL36"/>
-      <c r="AM36"/>
-      <c r="AN36"/>
-      <c r="AO36"/>
-      <c r="AP36"/>
-      <c r="AQ36"/>
-    </row>
-    <row r="37" spans="1:43" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="3"/>
-      <c r="B37" s="10"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37"/>
-      <c r="J37"/>
-      <c r="K37"/>
-      <c r="L37"/>
-      <c r="M37"/>
-      <c r="N37"/>
-      <c r="O37"/>
-      <c r="P37"/>
-      <c r="Q37"/>
-      <c r="R37"/>
-      <c r="S37"/>
-      <c r="T37"/>
-      <c r="U37"/>
-      <c r="V37"/>
-      <c r="W37"/>
-      <c r="X37"/>
-      <c r="Y37"/>
-      <c r="Z37"/>
-      <c r="AA37"/>
-      <c r="AB37"/>
-      <c r="AC37"/>
-      <c r="AD37"/>
-      <c r="AE37"/>
-      <c r="AF37"/>
-      <c r="AG37"/>
-      <c r="AH37"/>
-      <c r="AI37"/>
-      <c r="AJ37"/>
-      <c r="AK37"/>
-      <c r="AL37"/>
-      <c r="AM37"/>
-      <c r="AN37"/>
-      <c r="AO37"/>
-      <c r="AP37"/>
-      <c r="AQ37"/>
-    </row>
-    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="6"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-    </row>
-    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="6"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-    </row>
-    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="6"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-    </row>
-    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="6"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-    </row>
-    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="6"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-    </row>
-    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="6"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16"/>
-    </row>
-    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="6"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16"/>
-    </row>
-    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="6"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
-      <c r="H45" s="16"/>
-    </row>
-    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="6"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-      <c r="H46" s="16"/>
-    </row>
-    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="6"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
-      <c r="H47" s="16"/>
-    </row>
-    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="6"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16"/>
-    </row>
-    <row r="49" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="6"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="16"/>
-    </row>
-    <row r="50" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="6"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16"/>
-    </row>
-    <row r="51" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="6"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
-      <c r="H51" s="16"/>
-    </row>
-    <row r="52" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="6"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16"/>
-    </row>
-    <row r="53" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="6"/>
-      <c r="C53" s="16"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
-      <c r="G53" s="16"/>
-      <c r="H53" s="16"/>
-    </row>
-    <row r="54" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="6"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16"/>
-      <c r="H54" s="16"/>
-    </row>
-    <row r="55" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="6"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-    </row>
-    <row r="56" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="6"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
-      <c r="H56" s="16"/>
-    </row>
-    <row r="57" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="6"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
-      <c r="H57" s="16"/>
-    </row>
-    <row r="58" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="6"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="16"/>
-    </row>
-    <row r="59" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="6"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
-      <c r="H59" s="16"/>
-    </row>
-    <row r="60" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="6"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16"/>
-      <c r="H60" s="16"/>
-    </row>
-    <row r="61" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="6"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="16"/>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="16"/>
-      <c r="H61" s="16"/>
-    </row>
-    <row r="62" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="6"/>
-      <c r="C62" s="16"/>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="16"/>
-      <c r="H62" s="16"/>
-    </row>
-    <row r="63" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="6"/>
-      <c r="C63" s="16"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="F63" s="16"/>
-      <c r="G63" s="16"/>
-      <c r="H63" s="16"/>
-    </row>
-    <row r="64" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="6"/>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
-      <c r="H64" s="16"/>
-    </row>
-    <row r="65" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="6"/>
-      <c r="C65" s="16"/>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
-      <c r="H65" s="16"/>
-    </row>
-    <row r="66" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="6"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16"/>
-      <c r="H66" s="16"/>
-    </row>
-    <row r="67" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="6"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
-      <c r="H67" s="16"/>
-    </row>
-    <row r="68" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="6"/>
-      <c r="C68" s="16"/>
-      <c r="D68" s="16"/>
-      <c r="E68" s="16"/>
-      <c r="F68" s="16"/>
-      <c r="G68" s="16"/>
-      <c r="H68" s="16"/>
-    </row>
-    <row r="69" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="6"/>
-      <c r="C69" s="16"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16"/>
-      <c r="H69" s="16"/>
-    </row>
-    <row r="70" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="6"/>
-      <c r="C70" s="16"/>
-      <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="16"/>
-      <c r="H70" s="16"/>
-    </row>
-    <row r="71" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="6"/>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="16"/>
-      <c r="F71" s="16"/>
-      <c r="G71" s="16"/>
-      <c r="H71" s="16"/>
-    </row>
-    <row r="72" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="6"/>
-      <c r="C72" s="16"/>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="16"/>
-      <c r="H72" s="16"/>
-    </row>
-    <row r="73" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="6"/>
-      <c r="C73" s="16"/>
-      <c r="D73" s="16"/>
-      <c r="E73" s="16"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="16"/>
-      <c r="H73" s="16"/>
-    </row>
-    <row r="74" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="6"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="16"/>
-      <c r="H74" s="16"/>
-    </row>
-    <row r="75" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="6"/>
-      <c r="C75" s="16"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="16"/>
-      <c r="H75" s="16"/>
-    </row>
-    <row r="76" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="6"/>
-      <c r="C76" s="16"/>
-      <c r="D76" s="16"/>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16"/>
-      <c r="G76" s="16"/>
-      <c r="H76" s="16"/>
-    </row>
-    <row r="77" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="6"/>
-      <c r="C77" s="16"/>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
-      <c r="H77" s="16"/>
-    </row>
-    <row r="78" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="6"/>
-      <c r="C78" s="16"/>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="16"/>
-      <c r="H78" s="16"/>
-    </row>
-    <row r="79" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="6"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16"/>
-      <c r="H79" s="16"/>
-    </row>
-    <row r="80" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="6"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="16"/>
-      <c r="H80" s="16"/>
-    </row>
-    <row r="81" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="6"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
-      <c r="F81" s="16"/>
-      <c r="G81" s="16"/>
-      <c r="H81" s="16"/>
-    </row>
-    <row r="82" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="6"/>
-      <c r="C82" s="16"/>
-      <c r="D82" s="16"/>
-      <c r="E82" s="16"/>
-      <c r="F82" s="16"/>
-      <c r="G82" s="16"/>
-      <c r="H82" s="16"/>
-    </row>
-    <row r="83" spans="2:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="6"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
-      <c r="F83" s="16"/>
-      <c r="G83" s="16"/>
-      <c r="H83" s="16"/>
-    </row>
+    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="62" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="63" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="64" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="65" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="66" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="68" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="69" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="70" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="71" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="72" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="73" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="74" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="75" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="76" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="77" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="78" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="79" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="80" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="41" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="47" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/docs/tableau_synthese.xlsx
+++ b/docs/tableau_synthese.xlsx
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f78ac8c4115f8c98/Documents/_Bureau/BTS SIO - Nextech/Info/E5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f78ac8c4115f8c98/Documents/GitHub/chriiisrdz.github.io/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="8_{181E88D1-149F-4158-ABF1-535095BE27AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8105D1CB-C0B9-405A-AC8D-2DD81F8DEC3A}"/>
+  <xr:revisionPtr revIDLastSave="167" documentId="8_{181E88D1-149F-4158-ABF1-535095BE27AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38653CAC-9E66-4A94-A4F4-73AE60663595}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$34</definedName>
   </definedNames>
   <calcPr calcId="101716"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -158,36 +158,12 @@
     <t>Installation de poste informatique laboratoire</t>
   </si>
   <si>
-    <t xml:space="preserve">Mise en place infrastructure </t>
-  </si>
-  <si>
-    <t>Configuration switch Cisco</t>
-  </si>
-  <si>
-    <t>Configuration routeur Cisco</t>
-  </si>
-  <si>
-    <t>Mise en place solution de sauvegade Proxmox Backup Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Installation gestion de ticket (GLPI) </t>
-  </si>
-  <si>
-    <t>Mise en place de solution de super vision</t>
-  </si>
-  <si>
-    <t>Mise en place de firewall physique et virtuel</t>
-  </si>
-  <si>
     <t>Gestion du parc informatique (Service Now)</t>
   </si>
   <si>
     <t>Gestion de sauvegarde et restauration (Externalisation de bande LTO avec Dataprotector)</t>
   </si>
   <si>
-    <t>Mise en place Graylog</t>
-  </si>
-  <si>
     <t>01/04/2026 au 11/04/2026</t>
   </si>
   <si>
@@ -200,9 +176,6 @@
     <t>09/02/2026 au 10/02/2026</t>
   </si>
   <si>
-    <t>12/01/2026 au 16/01/2026</t>
-  </si>
-  <si>
     <t>01/12/2025  au 01/02/2026</t>
   </si>
   <si>
@@ -215,19 +188,40 @@
     <t>Vérification des KPI cyber (Extration et croisement des données)</t>
   </si>
   <si>
-    <t>☑☑☑☑☑☑</t>
-  </si>
-  <si>
-    <t>☑☑☑</t>
-  </si>
-  <si>
-    <t>☑☑☑☑</t>
-  </si>
-  <si>
     <t>Centre de formation : AVP CCI - Pertuis</t>
   </si>
   <si>
     <t>☑</t>
+  </si>
+  <si>
+    <t>☑☑</t>
+  </si>
+  <si>
+    <t>Mise en production d'une infrastructure de virtualisation</t>
+  </si>
+  <si>
+    <t>Mise en place de la stratégie de sauvegarde (PBS)</t>
+  </si>
+  <si>
+    <t>Configuration de la commutation locale (Switch Cisco)</t>
+  </si>
+  <si>
+    <t>Configuration du routage et des VLANs (Routeur Cisco)</t>
+  </si>
+  <si>
+    <t>Déploiement d'une solution de ticketing (GLPI)</t>
+  </si>
+  <si>
+    <t>Déploiement d'un annuaire multi-sites</t>
+  </si>
+  <si>
+    <t>01/01/2025 au 01/05/25</t>
+  </si>
+  <si>
+    <t>Sécurisation et interconnexion réseau (pfSense)</t>
+  </si>
+  <si>
+    <t>Déploiement d'une solution de centralisation des logs (Graylog)</t>
   </si>
 </sst>
 </file>
@@ -721,7 +715,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -786,13 +780,16 @@
     <xf numFmtId="14" fontId="11" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1173,69 +1170,69 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ81"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AQ80"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="70.44140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="43" width="11.44140625" customWidth="1"/>
-    <col min="44" max="16384" width="10.88671875" style="1"/>
+    <col min="5" max="8" width="18.7109375" style="1" customWidth="1"/>
+    <col min="9" max="43" width="11.42578125" customWidth="1"/>
+    <col min="44" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="25"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+      <c r="H1" s="26"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-    </row>
-    <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+    </row>
+    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="32" t="s">
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="33"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="34"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31"/>
+    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="32"/>
       <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
@@ -1246,23 +1243,23 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="44" t="s">
+    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="46"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="47"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="43" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1284,9 +1281,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35"/>
-      <c r="B7" s="43"/>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="36"/>
+      <c r="B7" s="44"/>
       <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
@@ -1341,17 +1338,17 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="36" t="s">
+    <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="39"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1388,29 +1385,23 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>52</v>
-      </c>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="23"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1447,23 +1438,21 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="24"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="23"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1500,23 +1489,23 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="24"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="23"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1553,21 +1542,23 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="24"/>
+      <c r="C12" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="23"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1604,21 +1595,21 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="24"/>
+      <c r="C13" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="23"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1655,21 +1646,21 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="24"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="23"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1706,21 +1697,21 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B15" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="24"/>
+      <c r="C15" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="23"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1757,21 +1748,23 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="24"/>
+        <v>52</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="23" t="s">
+        <v>42</v>
+      </c>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1808,9 +1801,9 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="11"/>
-      <c r="B17" s="10"/>
+      <c r="B17" s="25"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
@@ -1853,15 +1846,17 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16"/>
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A18" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="42"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1898,17 +1893,19 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="41"/>
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="16"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1945,16 +1942,14 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>54</v>
-      </c>
+      <c r="C20" s="15"/>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
@@ -1996,16 +1991,14 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>54</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="15"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
       <c r="F21" s="15"/>
@@ -2047,16 +2040,14 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>54</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
       <c r="F22" s="15"/>
@@ -2098,16 +2089,14 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>54</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="15"/>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
@@ -2149,16 +2138,14 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>54</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="15"/>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
       <c r="F24" s="15"/>
@@ -2200,16 +2187,10 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>54</v>
-      </c>
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="11"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="15"/>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
       <c r="F25" s="15"/>
@@ -2251,15 +2232,17 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="11"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="16"/>
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A26" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="42"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2296,17 +2279,19 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="41"/>
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="16"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2343,16 +2328,14 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>54</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="15"/>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
       <c r="F28" s="15"/>
@@ -2394,16 +2377,10 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>54</v>
-      </c>
+    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="11"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="15"/>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
       <c r="F29" s="15"/>
@@ -2445,7 +2422,7 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="11"/>
       <c r="B30" s="10"/>
       <c r="C30" s="15"/>
@@ -2490,7 +2467,7 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="11"/>
       <c r="B31" s="10"/>
       <c r="C31" s="15"/>
@@ -2535,7 +2512,7 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="11"/>
       <c r="B32" s="10"/>
       <c r="C32" s="15"/>
@@ -2580,15 +2557,15 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="11"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="16"/>
+    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="12"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="18"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
@@ -2625,15 +2602,15 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="12"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="18"/>
+    <row r="34" spans="1:43" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" s="5"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
       <c r="I34"/>
       <c r="J34"/>
       <c r="K34"/>
@@ -2670,104 +2647,59 @@
       <c r="AP34"/>
       <c r="AQ34"/>
     </row>
-    <row r="35" spans="1:43" s="2" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35"/>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35"/>
-      <c r="R35"/>
-      <c r="S35"/>
-      <c r="T35"/>
-      <c r="U35"/>
-      <c r="V35"/>
-      <c r="W35"/>
-      <c r="X35"/>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35"/>
-      <c r="AB35"/>
-      <c r="AC35"/>
-      <c r="AD35"/>
-      <c r="AE35"/>
-      <c r="AF35"/>
-      <c r="AG35"/>
-      <c r="AH35"/>
-      <c r="AI35"/>
-      <c r="AJ35"/>
-      <c r="AK35"/>
-      <c r="AL35"/>
-      <c r="AM35"/>
-      <c r="AN35"/>
-      <c r="AO35"/>
-      <c r="AP35"/>
-      <c r="AQ35"/>
-    </row>
-    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="62" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="63" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="64" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="67" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="68" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="69" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="70" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="71" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="72" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="73" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="75" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="76" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="77" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="78" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="62" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="63" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="64" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="65" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="66" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="68" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="69" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="70" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="71" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="72" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="73" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="74" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="75" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="76" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="77" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="78" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="80" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="G1:H1"/>
@@ -2779,7 +2711,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="47" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="46" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/docs/tableau_synthese.xlsx
+++ b/docs/tableau_synthese.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="167" documentId="8_{181E88D1-149F-4158-ABF1-535095BE27AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38653CAC-9E66-4A94-A4F4-73AE60663595}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>

--- a/docs/tableau_synthese.xlsx
+++ b/docs/tableau_synthese.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f78ac8c4115f8c98/Documents/GitHub/chriiisrdz.github.io/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="167" documentId="8_{181E88D1-149F-4158-ABF1-535095BE27AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38653CAC-9E66-4A94-A4F4-73AE60663595}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="8_{181E88D1-149F-4158-ABF1-535095BE27AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{447989B9-0E36-44C4-A36A-2C568CF4AC68}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -206,9 +206,6 @@
     <t>Configuration de la commutation locale (Switch Cisco)</t>
   </si>
   <si>
-    <t>Configuration du routage et des VLANs (Routeur Cisco)</t>
-  </si>
-  <si>
     <t>Déploiement d'une solution de ticketing (GLPI)</t>
   </si>
   <si>
@@ -222,6 +219,9 @@
   </si>
   <si>
     <t>Déploiement d'une solution de centralisation des logs (Graylog)</t>
+  </si>
+  <si>
+    <t>Configuration du Routage Périmétrique, NAT et VPN</t>
   </si>
 </sst>
 </file>
@@ -1440,10 +1440,10 @@
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="24" t="s">
         <v>49</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>50</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>42</v>
@@ -1544,7 +1544,7 @@
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>34</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>36</v>
@@ -1699,7 +1699,7 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>37</v>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="25" t="s">
         <v>33</v>

--- a/docs/tableau_synthese.xlsx
+++ b/docs/tableau_synthese.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f78ac8c4115f8c98/Documents/GitHub/chriiisrdz.github.io/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="8_{181E88D1-149F-4158-ABF1-535095BE27AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{447989B9-0E36-44C4-A36A-2C568CF4AC68}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="8_{181E88D1-149F-4158-ABF1-535095BE27AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5D28A5E-0D9B-42EB-913A-581918FEF949}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="55">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -222,6 +222,12 @@
   </si>
   <si>
     <t>Configuration du Routage Périmétrique, NAT et VPN</t>
+  </si>
+  <si>
+    <t>Sécurisation des flux internes et contrôle applicatif (Palo Alto)</t>
+  </si>
+  <si>
+    <t>01/02/2026 au 16/03/2026</t>
   </si>
 </sst>
 </file>
@@ -792,9 +798,48 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -817,45 +862,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1183,56 +1189,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="26"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="33" t="s">
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="28"/>
-      <c r="H3" s="34"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="47"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="32"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
       <c r="F4" s="14" t="s">
         <v>8</v>
       </c>
@@ -1244,22 +1250,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="47"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="39"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="35" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1282,8 +1288,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="36"/>
-      <c r="B7" s="44"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="36"/>
       <c r="C7" s="20" t="s">
         <v>9</v>
       </c>
@@ -1339,16 +1345,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="39"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1802,14 +1808,24 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="16"/>
+      <c r="A17" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="22"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1847,16 +1863,16 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A18" s="40" t="s">
+      <c r="A18" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="42"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="34"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -2233,16 +2249,16 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A26" s="40" t="s">
+      <c r="A26" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="42"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="34"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2695,6 +2711,11 @@
     <row r="80" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2702,11 +2723,6 @@
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/docs/tableau_synthese.xlsx
+++ b/docs/tableau_synthese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f78ac8c4115f8c98/Documents/GitHub/chriiisrdz.github.io/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="188" documentId="8_{181E88D1-149F-4158-ABF1-535095BE27AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5D28A5E-0D9B-42EB-913A-581918FEF949}"/>
+  <xr:revisionPtr revIDLastSave="244" documentId="8_{181E88D1-149F-4158-ABF1-535095BE27AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17CECB16-93AA-4E59-BDFA-65908CD49F7D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="56">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -152,9 +152,6 @@
     <t xml:space="preserve">Mise en place switch </t>
   </si>
   <si>
-    <t>Vérification des KPI cyber</t>
-  </si>
-  <si>
     <t>Installation de poste informatique laboratoire</t>
   </si>
   <si>
@@ -228,6 +225,12 @@
   </si>
   <si>
     <t>01/02/2026 au 16/03/2026</t>
+  </si>
+  <si>
+    <t>Routine journaliere</t>
+  </si>
+  <si>
+    <t>04/11/2024 au 04/09/2026</t>
   </si>
 </sst>
 </file>
@@ -747,9 +750,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -798,15 +798,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -840,29 +864,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1189,83 +1192,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="46" t="s">
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="41"/>
-      <c r="H3" s="47"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="33"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="14" t="s">
+      <c r="A4" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="18" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="39"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="46"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="42" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1288,15 +1291,15 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="27"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="20" t="s">
+      <c r="A7" s="35"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="19" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="19" t="s">
         <v>11</v>
       </c>
       <c r="F7" s="8" t="s">
@@ -1305,7 +1308,7 @@
       <c r="G7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="47" t="s">
         <v>14</v>
       </c>
       <c r="I7"/>
@@ -1345,16 +1348,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="31"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1392,22 +1395,22 @@
       <c r="AQ8"/>
     </row>
     <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="23"/>
+      <c r="A9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="22"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1445,20 +1448,20 @@
       <c r="AQ9"/>
     </row>
     <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="23"/>
+      <c r="C10" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="22"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1496,22 +1499,22 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="23"/>
+      <c r="A11" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="22"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1549,22 +1552,22 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12" s="23"/>
+      <c r="A12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="22"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1602,20 +1605,20 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="23"/>
+      <c r="A13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="22"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1653,20 +1656,20 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="23"/>
+      <c r="A14" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1704,20 +1707,20 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="23"/>
+      <c r="A15" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="22"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1755,21 +1758,21 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="23" t="s">
-        <v>42</v>
+      <c r="A16" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22" t="s">
+        <v>41</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -1808,24 +1811,24 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="22" t="s">
+      <c r="C17" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" s="22"/>
+      <c r="D17" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" s="21"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1863,16 +1866,16 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="34"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="41"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1910,18 +1913,22 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="16"/>
+      <c r="A19" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="22"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1959,18 +1966,28 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
+      <c r="B20" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>41</v>
+      </c>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -2008,18 +2025,28 @@
       <c r="AQ20"/>
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="16"/>
+      <c r="B21" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="21"/>
+      <c r="H21" s="22" t="s">
+        <v>41</v>
+      </c>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -2057,18 +2084,20 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="16"/>
+      <c r="A22" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="22"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2106,18 +2135,24 @@
       <c r="AQ22"/>
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="25" t="s">
+      <c r="A23" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="16"/>
+      <c r="B23" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2155,18 +2190,26 @@
       <c r="AQ23"/>
     </row>
     <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="16"/>
+      <c r="A24" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G24" s="21"/>
+      <c r="H24" s="22" t="s">
+        <v>41</v>
+      </c>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2204,14 +2247,22 @@
       <c r="AQ24"/>
     </row>
     <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="11"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="16"/>
+      <c r="A25" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="22"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2249,16 +2300,16 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="34"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="41"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2296,18 +2347,22 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="16"/>
+      <c r="B27" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="22" t="s">
+        <v>41</v>
+      </c>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2345,18 +2400,14 @@
       <c r="AQ27"/>
     </row>
     <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B28" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="16"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="22"/>
       <c r="I28"/>
       <c r="J28"/>
       <c r="K28"/>
@@ -2394,14 +2445,14 @@
       <c r="AQ28"/>
     </row>
     <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="11"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="16"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="15"/>
       <c r="I29"/>
       <c r="J29"/>
       <c r="K29"/>
@@ -2439,14 +2490,14 @@
       <c r="AQ29"/>
     </row>
     <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="11"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="16"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="15"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
@@ -2484,14 +2535,14 @@
       <c r="AQ30"/>
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="11"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="16"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="15"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
@@ -2529,14 +2580,14 @@
       <c r="AQ31"/>
     </row>
     <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="11"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="16"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="15"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
@@ -2574,14 +2625,14 @@
       <c r="AQ32"/>
     </row>
     <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="12"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="18"/>
+      <c r="A33" s="11"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="17"/>
       <c r="I33"/>
       <c r="J33"/>
       <c r="K33"/>
@@ -2711,11 +2762,6 @@
     <row r="80" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2723,6 +2769,11 @@
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/docs/tableau_synthese.xlsx
+++ b/docs/tableau_synthese.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f78ac8c4115f8c98/Documents/GitHub/chriiisrdz.github.io/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="244" documentId="8_{181E88D1-149F-4158-ABF1-535095BE27AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17CECB16-93AA-4E59-BDFA-65908CD49F7D}"/>
+  <xr:revisionPtr revIDLastSave="258" documentId="8_{181E88D1-149F-4158-ABF1-535095BE27AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2928251B-65F1-40FC-919B-6717F0EC14C9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$34</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="57">
   <si>
     <t>Gérer le patrimoine informatique</t>
   </si>
@@ -209,9 +210,6 @@
     <t>Déploiement d'un annuaire multi-sites</t>
   </si>
   <si>
-    <t>01/01/2025 au 01/05/25</t>
-  </si>
-  <si>
     <t>Sécurisation et interconnexion réseau (pfSense)</t>
   </si>
   <si>
@@ -231,6 +229,12 @@
   </si>
   <si>
     <t>04/11/2024 au 04/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>01/01/2025 au 01/05/2025</t>
   </si>
 </sst>
 </file>
@@ -798,6 +802,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -863,9 +870,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1180,68 +1184,69 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AQ80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="70.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="18.7109375" style="1" customWidth="1"/>
-    <col min="9" max="43" width="11.42578125" customWidth="1"/>
-    <col min="44" max="16384" width="10.85546875" style="1"/>
+    <col min="5" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="43" width="11.44140625" customWidth="1"/>
+    <col min="44" max="16384" width="10.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="25"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="H1" s="26"/>
+      <c r="AQ1" s="1"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-    </row>
-    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="26" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+    </row>
+    <row r="3" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="32" t="s">
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="33"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="34"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="29" t="s">
+    <row r="4" spans="1:43" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="32"/>
       <c r="F4" s="13" t="s">
         <v>8</v>
       </c>
@@ -1252,23 +1257,23 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
+    <row r="5" spans="1:43" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="46"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="34" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="47"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="43" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1290,9 +1295,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="35"/>
-      <c r="B7" s="43"/>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.89999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="36"/>
+      <c r="B7" s="44"/>
       <c r="C7" s="19" t="s">
         <v>9</v>
       </c>
@@ -1308,7 +1313,7 @@
       <c r="G7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="47" t="s">
+      <c r="H7" s="25" t="s">
         <v>14</v>
       </c>
       <c r="I7"/>
@@ -1347,17 +1352,17 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="36" t="s">
+    <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="39"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1394,7 +1399,7 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>43</v>
       </c>
@@ -1447,12 +1452,12 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>41</v>
@@ -1498,7 +1503,7 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>45</v>
       </c>
@@ -1551,9 +1556,9 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="23" t="s">
         <v>33</v>
@@ -1604,7 +1609,7 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>44</v>
       </c>
@@ -1655,7 +1660,7 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>46</v>
       </c>
@@ -1706,9 +1711,9 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B15" s="23" t="s">
         <v>36</v>
@@ -1757,9 +1762,9 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>32</v>
@@ -1810,12 +1815,12 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="24" t="s">
         <v>52</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>53</v>
       </c>
       <c r="C17" s="21" t="s">
         <v>42</v>
@@ -1865,17 +1870,17 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A18" s="39" t="s">
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A18" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="41"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="42"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1912,7 +1917,7 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>31</v>
       </c>
@@ -1965,7 +1970,7 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>26</v>
       </c>
@@ -2024,7 +2029,7 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>27</v>
       </c>
@@ -2083,7 +2088,7 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>30</v>
       </c>
@@ -2134,7 +2139,7 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>39</v>
       </c>
@@ -2189,7 +2194,7 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>29</v>
       </c>
@@ -2246,12 +2251,12 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="24" t="s">
         <v>54</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>55</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>41</v>
@@ -2299,17 +2304,17 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A26" s="39" t="s">
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A26" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="41"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="42"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2346,7 +2351,7 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>28</v>
       </c>
@@ -2361,7 +2366,7 @@
       <c r="F27" s="21"/>
       <c r="G27" s="21"/>
       <c r="H27" s="22" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="I27"/>
       <c r="J27"/>
@@ -2399,7 +2404,7 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10"/>
       <c r="B28" s="24"/>
       <c r="C28" s="21"/>
@@ -2444,7 +2449,7 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10"/>
       <c r="B29" s="9"/>
       <c r="C29" s="14"/>
@@ -2489,7 +2494,7 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10"/>
       <c r="B30" s="9"/>
       <c r="C30" s="14"/>
@@ -2534,7 +2539,7 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10"/>
       <c r="B31" s="9"/>
       <c r="C31" s="14"/>
@@ -2579,7 +2584,7 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10"/>
       <c r="B32" s="9"/>
       <c r="C32" s="14"/>
@@ -2624,7 +2629,7 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11"/>
       <c r="B33" s="12"/>
       <c r="C33" s="16"/>
@@ -2669,7 +2674,7 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:43" s="2" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
       <c r="B34" s="3"/>
       <c r="C34" s="4"/>
@@ -2714,52 +2719,52 @@
       <c r="AP34"/>
       <c r="AQ34"/>
     </row>
-    <row r="35" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="62" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="63" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="64" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="67" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="68" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="69" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="70" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="71" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="72" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="73" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="75" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="76" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="77" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="78" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="35" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="57" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="62" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="63" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="64" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="65" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="66" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="67" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="68" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="69" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="70" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="71" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="72" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="73" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="74" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="75" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="76" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="77" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="78" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="79" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="80" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A6:A7"/>
@@ -2781,4 +2786,371 @@
   <pageSetup paperSize="9" scale="46" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DC7D070-A38F-4640-81B0-1D810CE34E9A}">
+  <dimension ref="A1:H34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="11.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="24.6" x14ac:dyDescent="0.25">
+      <c r="A1" s="26"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+    </row>
+    <row r="2" spans="1:8" ht="25.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+    </row>
+    <row r="3" spans="1:8" ht="22.8" x14ac:dyDescent="0.25">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="22.8" x14ac:dyDescent="0.25">
+      <c r="A4" s="30"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="18"/>
+    </row>
+    <row r="5" spans="1:8" ht="23.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="45"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="47"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="35"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="36"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="25"/>
+    </row>
+    <row r="8" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A8" s="37"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="39"/>
+    </row>
+    <row r="9" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="22"/>
+    </row>
+    <row r="10" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="22"/>
+    </row>
+    <row r="11" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="22"/>
+    </row>
+    <row r="12" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
+    </row>
+    <row r="13" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A13" s="10"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="22"/>
+    </row>
+    <row r="14" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A14" s="10"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
+    </row>
+    <row r="15" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="22"/>
+    </row>
+    <row r="16" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
+    </row>
+    <row r="17" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A17" s="10"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+    </row>
+    <row r="18" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A18" s="40"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="42"/>
+    </row>
+    <row r="19" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="22"/>
+    </row>
+    <row r="20" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="22"/>
+    </row>
+    <row r="21" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A21" s="10"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="22"/>
+    </row>
+    <row r="22" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A22" s="10"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="22"/>
+    </row>
+    <row r="23" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A23" s="10"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="22"/>
+    </row>
+    <row r="24" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A24" s="10"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="22"/>
+    </row>
+    <row r="25" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A25" s="10"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="22"/>
+    </row>
+    <row r="26" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A26" s="40"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="42"/>
+    </row>
+    <row r="27" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A27" s="10"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="22"/>
+    </row>
+    <row r="28" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A28" s="10"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="22"/>
+    </row>
+    <row r="29" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A29" s="10"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="15"/>
+    </row>
+    <row r="30" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A30" s="10"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="15"/>
+    </row>
+    <row r="31" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A31" s="10"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="15"/>
+    </row>
+    <row r="32" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A32" s="10"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="15"/>
+    </row>
+    <row r="33" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="11"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="17"/>
+    </row>
+    <row r="34" spans="1:8" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A18:H18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>